--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-08-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EAED48-40C0-4372-A20E-C8011380E889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950A4AF6-AB3D-4020-925B-AB44B0D1B4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31710" yWindow="750" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33075" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="375">
   <si>
     <t>SKU</t>
   </si>
@@ -742,9 +742,6 @@
     <t>£64.38</t>
   </si>
   <si>
-    <t>£71.04</t>
-  </si>
-  <si>
     <t>£52.0</t>
   </si>
   <si>
@@ -778,9 +775,6 @@
     <t>£72.69</t>
   </si>
   <si>
-    <t>£95.5</t>
-  </si>
-  <si>
     <t>£55.9</t>
   </si>
   <si>
@@ -811,9 +805,6 @@
     <t>£75.76</t>
   </si>
   <si>
-    <t>£84.22</t>
-  </si>
-  <si>
     <t>£60.99</t>
   </si>
   <si>
@@ -964,9 +955,6 @@
     <t>£2208.32</t>
   </si>
   <si>
-    <t>£111.12</t>
-  </si>
-  <si>
     <t>£1743.68</t>
   </si>
   <si>
@@ -997,9 +985,6 @@
     <t>£2057.12</t>
   </si>
   <si>
-    <t>£153.89</t>
-  </si>
-  <si>
     <t>£2053.92</t>
   </si>
   <si>
@@ -1030,9 +1015,6 @@
     <t>£2183.04</t>
   </si>
   <si>
-    <t>£172.26</t>
-  </si>
-  <si>
     <t>£2006.4</t>
   </si>
   <si>
@@ -1151,6 +1133,18 @@
   </si>
   <si>
     <t>£1972.64</t>
+  </si>
+  <si>
+    <t>£65.56</t>
+  </si>
+  <si>
+    <t>£1777.92</t>
+  </si>
+  <si>
+    <t>£2462.24</t>
+  </si>
+  <si>
+    <t>£2756.16</t>
   </si>
 </sst>
 </file>
@@ -1616,7 +1610,7 @@
         <v>28</v>
       </c>
       <c r="O2" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="P2" t="s">
         <v>29</v>
@@ -1728,7 +1722,7 @@
         <v>53</v>
       </c>
       <c r="O4" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="P4" t="s">
         <v>54</v>
@@ -1769,7 +1763,7 @@
         <v>62</v>
       </c>
       <c r="J5" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="K5" t="s">
         <v>63</v>
@@ -1825,7 +1819,7 @@
         <v>74</v>
       </c>
       <c r="J6" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="K6" t="s">
         <v>75</v>
@@ -1840,7 +1834,7 @@
         <v>77</v>
       </c>
       <c r="O6" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="P6" t="s">
         <v>78</v>
@@ -1896,7 +1890,7 @@
         <v>90</v>
       </c>
       <c r="O7" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="P7" t="s">
         <v>91</v>
@@ -1993,7 +1987,7 @@
         <v>111</v>
       </c>
       <c r="J9" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="K9" t="s">
         <v>112</v>
@@ -2049,7 +2043,7 @@
         <v>122</v>
       </c>
       <c r="J10" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="K10" t="s">
         <v>123</v>
@@ -2064,7 +2058,7 @@
         <v>125</v>
       </c>
       <c r="O10" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="P10" t="s">
         <v>126</v>
@@ -2105,7 +2099,7 @@
         <v>133</v>
       </c>
       <c r="J11" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="K11" t="s">
         <v>123</v>
@@ -2176,7 +2170,7 @@
         <v>148</v>
       </c>
       <c r="O12" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="P12" t="s">
         <v>149</v>
@@ -2217,7 +2211,7 @@
         <v>157</v>
       </c>
       <c r="J13" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="K13" t="s">
         <v>158</v>
@@ -2232,7 +2226,7 @@
         <v>160</v>
       </c>
       <c r="O13" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="P13" t="s">
         <v>161</v>
@@ -2273,7 +2267,7 @@
         <v>169</v>
       </c>
       <c r="J14" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="K14" t="s">
         <v>170</v>
@@ -2288,7 +2282,7 @@
         <v>172</v>
       </c>
       <c r="O14" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="P14" t="s">
         <v>166</v>
@@ -2317,7 +2311,7 @@
         <v>143</v>
       </c>
       <c r="F15" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="G15" t="s">
         <v>177</v>
@@ -2329,7 +2323,7 @@
         <v>179</v>
       </c>
       <c r="J15" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="K15" t="s">
         <v>180</v>
@@ -2385,7 +2379,7 @@
         <v>190</v>
       </c>
       <c r="J16" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="K16" t="s">
         <v>191</v>
@@ -2400,7 +2394,7 @@
         <v>193</v>
       </c>
       <c r="O16" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="P16" t="s">
         <v>194</v>
@@ -2456,7 +2450,7 @@
         <v>204</v>
       </c>
       <c r="O17" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="P17" t="s">
         <v>205</v>
@@ -2512,7 +2506,7 @@
         <v>216</v>
       </c>
       <c r="O18" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="P18" t="s">
         <v>217</v>
@@ -2541,7 +2535,7 @@
         <v>222</v>
       </c>
       <c r="F19" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="G19" t="s">
         <v>223</v>
@@ -2553,7 +2547,7 @@
         <v>225</v>
       </c>
       <c r="J19" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="K19" t="s">
         <v>226</v>
@@ -2597,7 +2591,7 @@
         <v>234</v>
       </c>
       <c r="F20" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="G20" t="s">
         <v>235</v>
@@ -2621,83 +2615,83 @@
         <v>239</v>
       </c>
       <c r="N20" t="s">
+        <v>228</v>
+      </c>
+      <c r="O20" t="s">
+        <v>364</v>
+      </c>
+      <c r="P20" t="s">
         <v>240</v>
-      </c>
-      <c r="O20" t="s">
-        <v>370</v>
-      </c>
-      <c r="P20" t="s">
-        <v>241</v>
       </c>
       <c r="Q20" t="s">
         <v>234</v>
       </c>
       <c r="R20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>242</v>
+      </c>
+      <c r="B21" t="s">
         <v>243</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>244</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>244</v>
+      </c>
+      <c r="E21" t="s">
+        <v>244</v>
+      </c>
+      <c r="F21" t="s">
+        <v>336</v>
+      </c>
+      <c r="G21" t="s">
         <v>245</v>
       </c>
-      <c r="D21" t="s">
-        <v>245</v>
-      </c>
-      <c r="E21" t="s">
-        <v>245</v>
-      </c>
-      <c r="F21" t="s">
-        <v>342</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>246</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>247</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>248</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>249</v>
-      </c>
-      <c r="K21" t="s">
-        <v>250</v>
       </c>
       <c r="L21" t="s">
         <v>21</v>
       </c>
       <c r="M21" t="s">
+        <v>250</v>
+      </c>
+      <c r="N21" t="s">
+        <v>228</v>
+      </c>
+      <c r="O21" t="s">
+        <v>365</v>
+      </c>
+      <c r="P21" t="s">
         <v>251</v>
       </c>
-      <c r="N21" t="s">
+      <c r="Q21" t="s">
+        <v>244</v>
+      </c>
+      <c r="R21" t="s">
         <v>252</v>
-      </c>
-      <c r="O21" t="s">
-        <v>371</v>
-      </c>
-      <c r="P21" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>245</v>
-      </c>
-      <c r="R21" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B22" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C22" t="s">
         <v>177</v>
@@ -2709,172 +2703,172 @@
         <v>177</v>
       </c>
       <c r="F22" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="G22" t="s">
+        <v>255</v>
+      </c>
+      <c r="H22" t="s">
+        <v>256</v>
+      </c>
+      <c r="I22" t="s">
         <v>257</v>
       </c>
-      <c r="H22" t="s">
+      <c r="J22" t="s">
         <v>258</v>
       </c>
-      <c r="I22" t="s">
+      <c r="K22" t="s">
         <v>259</v>
-      </c>
-      <c r="J22" t="s">
-        <v>260</v>
-      </c>
-      <c r="K22" t="s">
-        <v>261</v>
       </c>
       <c r="L22" t="s">
         <v>21</v>
       </c>
       <c r="M22" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N22" t="s">
-        <v>263</v>
+        <v>371</v>
       </c>
       <c r="O22" t="s">
         <v>177</v>
       </c>
       <c r="P22" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Q22" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="R22" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C23" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D23" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E23" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F23" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="G23" t="s">
         <v>143</v>
       </c>
       <c r="H23" t="s">
+        <v>267</v>
+      </c>
+      <c r="I23" t="s">
+        <v>268</v>
+      </c>
+      <c r="J23" t="s">
+        <v>269</v>
+      </c>
+      <c r="K23" t="s">
         <v>270</v>
-      </c>
-      <c r="I23" t="s">
-        <v>271</v>
-      </c>
-      <c r="J23" t="s">
-        <v>272</v>
-      </c>
-      <c r="K23" t="s">
-        <v>273</v>
       </c>
       <c r="L23" t="s">
         <v>21</v>
       </c>
       <c r="M23" t="s">
+        <v>271</v>
+      </c>
+      <c r="N23" t="s">
+        <v>272</v>
+      </c>
+      <c r="O23" t="s">
+        <v>266</v>
+      </c>
+      <c r="P23" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>273</v>
+      </c>
+      <c r="R23" t="s">
         <v>274</v>
-      </c>
-      <c r="N23" t="s">
-        <v>275</v>
-      </c>
-      <c r="O23" t="s">
-        <v>269</v>
-      </c>
-      <c r="P23" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>276</v>
-      </c>
-      <c r="R23" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B24" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C24" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D24" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E24" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F24" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="G24" t="s">
         <v>143</v>
       </c>
       <c r="H24" t="s">
+        <v>278</v>
+      </c>
+      <c r="I24" t="s">
+        <v>279</v>
+      </c>
+      <c r="J24" t="s">
+        <v>280</v>
+      </c>
+      <c r="K24" t="s">
         <v>281</v>
-      </c>
-      <c r="I24" t="s">
-        <v>282</v>
-      </c>
-      <c r="J24" t="s">
-        <v>283</v>
-      </c>
-      <c r="K24" t="s">
-        <v>284</v>
       </c>
       <c r="L24" t="s">
         <v>21</v>
       </c>
       <c r="M24" t="s">
+        <v>282</v>
+      </c>
+      <c r="N24" t="s">
+        <v>283</v>
+      </c>
+      <c r="O24" t="s">
+        <v>277</v>
+      </c>
+      <c r="P24" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q24" t="s">
         <v>285</v>
       </c>
-      <c r="N24" t="s">
+      <c r="R24" t="s">
         <v>286</v>
-      </c>
-      <c r="O24" t="s">
-        <v>280</v>
-      </c>
-      <c r="P24" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>288</v>
-      </c>
-      <c r="R24" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B25" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C25" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D25" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E25" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F25" t="s">
         <v>143</v>
@@ -2889,7 +2883,7 @@
         <v>143</v>
       </c>
       <c r="J25" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="K25" t="s">
         <v>143</v>
@@ -2898,13 +2892,13 @@
         <v>143</v>
       </c>
       <c r="M25" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="N25" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="O25" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="P25" t="s">
         <v>143</v>
@@ -2918,226 +2912,226 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B26" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C26" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D26" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E26" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F26" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="G26" t="s">
         <v>143</v>
       </c>
       <c r="H26" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I26" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J26" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="K26" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="L26" t="s">
         <v>21</v>
       </c>
       <c r="M26" t="s">
+        <v>299</v>
+      </c>
+      <c r="N26" t="s">
+        <v>300</v>
+      </c>
+      <c r="O26" t="s">
+        <v>367</v>
+      </c>
+      <c r="P26" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q26" t="s">
         <v>302</v>
       </c>
-      <c r="N26" t="s">
+      <c r="R26" t="s">
         <v>303</v>
-      </c>
-      <c r="O26" t="s">
-        <v>373</v>
-      </c>
-      <c r="P26" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>305</v>
-      </c>
-      <c r="R26" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B27" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C27" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D27" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E27" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F27" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="G27" t="s">
         <v>143</v>
       </c>
       <c r="H27" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="I27" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="J27" t="s">
         <v>143</v>
       </c>
       <c r="K27" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="L27" t="s">
         <v>21</v>
       </c>
       <c r="M27" t="s">
+        <v>310</v>
+      </c>
+      <c r="N27" t="s">
+        <v>372</v>
+      </c>
+      <c r="O27" t="s">
+        <v>368</v>
+      </c>
+      <c r="P27" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>312</v>
+      </c>
+      <c r="R27" t="s">
         <v>313</v>
-      </c>
-      <c r="N27" t="s">
-        <v>314</v>
-      </c>
-      <c r="O27" t="s">
-        <v>374</v>
-      </c>
-      <c r="P27" t="s">
-        <v>315</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>316</v>
-      </c>
-      <c r="R27" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B28" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C28" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D28" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E28" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F28" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="G28" t="s">
         <v>143</v>
       </c>
       <c r="H28" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="I28" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J28" t="s">
         <v>143</v>
       </c>
       <c r="K28" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="L28" t="s">
         <v>21</v>
       </c>
       <c r="M28" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="N28" t="s">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="O28" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="P28" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="Q28" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="R28" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B29" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C29" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D29" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E29" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="F29" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="G29" t="s">
         <v>143</v>
       </c>
       <c r="H29" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="I29" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J29" t="s">
         <v>143</v>
       </c>
       <c r="K29" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="L29" t="s">
         <v>143</v>
       </c>
       <c r="M29" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="N29" t="s">
-        <v>336</v>
+        <v>374</v>
       </c>
       <c r="O29" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="P29" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="Q29" t="s">
         <v>143</v>
       </c>
       <c r="R29" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
